--- a/HomeSOC Reference Sheet.xlsx
+++ b/HomeSOC Reference Sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ee7298f1c91c137/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\HomeSOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{5100CDA7-91EE-4731-8E0F-DBC32F187D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0B2FD5B-3954-43CA-979B-252258312DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="434">
   <si>
     <t>Home SOC Operations Manual</t>
   </si>
@@ -100,262 +100,1177 @@
     <t>Detect, triage, and document home-network security events</t>
   </si>
   <si>
-    <t>Netdata + Uptime Kuma active; Grafana paused</t>
+    <t>Operating Principles</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Keep the Home SOC boring, observable, and recoverable.</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Prefer read-only monitoring where possible; document any blocking/active-response controls before enabling them.</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Do not store real passwords, API tokens, or private keys in this workbook.</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Every alert should end in one of three outcomes: benign, action taken, or backlog item.</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Back up configs before major changes and record the change in the Change Log.</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Keep Raspberry Pi patching and storage health visible; small systems fail quietly.</t>
+  </si>
+  <si>
+    <t>Asset ID</t>
+  </si>
+  <si>
+    <t>Asset Name</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>IP / Hostname</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Criticality</t>
+  </si>
+  <si>
+    <t>Backup?</t>
+  </si>
+  <si>
+    <t>Monitoring?</t>
+  </si>
+  <si>
+    <t>SOC-PI-01</t>
+  </si>
+  <si>
+    <t>Raspberry Pi SOC Host</t>
+  </si>
+  <si>
+    <t>Server</t>
+  </si>
+  <si>
+    <t>raspberrypi.local / TBD</t>
+  </si>
+  <si>
+    <t>Home LAN</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Core host for Home SOC services and logs.</t>
+  </si>
+  <si>
+    <t>NET-RTR-01</t>
+  </si>
+  <si>
+    <t>Home Router / Firewall</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>Gateway IP TBD</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Config export</t>
+  </si>
+  <si>
+    <t>Primary ingress/egress visibility point.</t>
+  </si>
+  <si>
+    <t>NAS-LOG-01</t>
+  </si>
+  <si>
+    <t>External SSD / Log Storage</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Local mount TBD</t>
+  </si>
+  <si>
+    <t>Track free space and SMART/health status.</t>
+  </si>
+  <si>
+    <t>ENDPOINTS</t>
+  </si>
+  <si>
+    <t>Family Devices</t>
+  </si>
+  <si>
+    <t>Endpoint Group</t>
+  </si>
+  <si>
+    <t>DHCP range TBD</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>Group record; split into devices as needed.</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Host/Container</t>
+  </si>
+  <si>
+    <t>Port(s)</t>
+  </si>
+  <si>
+    <t>Data Path</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Restart Policy</t>
+  </si>
+  <si>
+    <t>Health Check</t>
+  </si>
+  <si>
+    <t>Portainer</t>
+  </si>
+  <si>
+    <t>Docker management</t>
+  </si>
+  <si>
+    <t>Docker container</t>
+  </si>
+  <si>
+    <t>9443/TCP</t>
+  </si>
+  <si>
+    <t>Docker volume</t>
+  </si>
+  <si>
+    <t>Running</t>
+  </si>
+  <si>
+    <t>unless-stopped</t>
+  </si>
+  <si>
+    <t>Portainer UI loads</t>
+  </si>
+  <si>
+    <t>Primary management interface for lab containers.</t>
+  </si>
+  <si>
+    <t>Netdata</t>
+  </si>
+  <si>
+    <t>System monitoring and dashboard</t>
+  </si>
+  <si>
+    <t>19999/TCP</t>
+  </si>
+  <si>
+    <t>Netdata dashboard loads</t>
+  </si>
+  <si>
+    <t>Current monitoring dashboard for the Raspberry Pi host.</t>
+  </si>
+  <si>
+    <t>Uptime Kuma</t>
+  </si>
+  <si>
+    <t>Service uptime monitoring</t>
+  </si>
+  <si>
+    <t>3001/TCP</t>
+  </si>
+  <si>
+    <t>Monitors report current service state</t>
+  </si>
+  <si>
+    <t>Used to track Home SOC service availability.</t>
+  </si>
+  <si>
+    <t>Grafana</t>
+  </si>
+  <si>
+    <t>Visualization</t>
+  </si>
+  <si>
+    <t>3000/TCP</t>
+  </si>
+  <si>
+    <t>Installed (Paused)</t>
+  </si>
+  <si>
+    <t>Container installed but intentionally paused</t>
+  </si>
+  <si>
+    <t>Deferred until Prometheus or additional data sources justify it.</t>
+  </si>
+  <si>
+    <t>Prometheus</t>
+  </si>
+  <si>
+    <t>Metrics backend for Grafana</t>
+  </si>
+  <si>
+    <t>Not installed</t>
+  </si>
+  <si>
+    <t>Deferred</t>
+  </si>
+  <si>
+    <t>Deferred by design</t>
+  </si>
+  <si>
+    <t>Netdata meets current monitoring needs.</t>
+  </si>
+  <si>
+    <t>Wazuh</t>
+  </si>
+  <si>
+    <t>SIEM / endpoint security monitoring</t>
+  </si>
+  <si>
+    <t>Planned</t>
+  </si>
+  <si>
+    <t>Architecture decision pending</t>
+  </si>
+  <si>
+    <t>Future SIEM candidate; do not document as installed yet.</t>
+  </si>
+  <si>
+    <t>Path / Zone</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>Protocol / Port</t>
+  </si>
+  <si>
+    <t>Allowed?</t>
+  </si>
+  <si>
+    <t>Auth Method</t>
+  </si>
+  <si>
+    <t>Logging</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>Review Cadence</t>
+  </si>
+  <si>
+    <t>Admin SSH</t>
+  </si>
+  <si>
+    <t>Josh admin device</t>
+  </si>
+  <si>
+    <t>SSH / 22 or custom</t>
+  </si>
+  <si>
+    <t>Key-based</t>
+  </si>
+  <si>
+    <t>Auth logs</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>Disable password SSH after key validation.</t>
+  </si>
+  <si>
+    <t>Netdata local</t>
+  </si>
+  <si>
+    <t>HTTP / 19999</t>
+  </si>
+  <si>
+    <t>Local trusted access</t>
+  </si>
+  <si>
+    <t>Netdata logs</t>
+  </si>
+  <si>
+    <t>Keep local only unless a protected access path is added.</t>
+  </si>
+  <si>
+    <t>Portainer local</t>
+  </si>
+  <si>
+    <t>HTTPS / 9443</t>
+  </si>
+  <si>
+    <t>Local account</t>
+  </si>
+  <si>
+    <t>Portainer logs</t>
+  </si>
+  <si>
+    <t>Protect carefully because it can manage containers.</t>
+  </si>
+  <si>
+    <t>Uptime Kuma local</t>
+  </si>
+  <si>
+    <t>HTTP / 3001</t>
+  </si>
+  <si>
+    <t>App logs</t>
+  </si>
+  <si>
+    <t>Used for availability checks.</t>
+  </si>
+  <si>
+    <t>Remote access</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>Home SOC</t>
+  </si>
+  <si>
+    <t>VPN only</t>
+  </si>
+  <si>
+    <t>MFA / keys</t>
+  </si>
+  <si>
+    <t>VPN logs</t>
+  </si>
+  <si>
+    <t>Avoid direct public dashboard exposure.</t>
+  </si>
+  <si>
+    <t>Syslog ingest</t>
+  </si>
+  <si>
+    <t>Network devices</t>
+  </si>
+  <si>
+    <t>Log collector</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>No log collector is installed yet; leave blank until Loki or another collector is selected.</t>
+  </si>
+  <si>
+    <t>Cadence</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Procedure</t>
+  </si>
+  <si>
+    <t>Last Done</t>
+  </si>
+  <si>
+    <t>Evidence / Notes</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>Review alert queue</t>
+  </si>
+  <si>
+    <t>Check new high/critical alerts and unresolved items.</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Check SOC host health</t>
+  </si>
+  <si>
+    <t>CPU, memory, disk, temperature, and service uptime.</t>
+  </si>
+  <si>
+    <t>Confirm log freshness</t>
+  </si>
+  <si>
+    <t>Verify latest logs arrived within expected window.</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>Review dashboard trends</t>
+  </si>
+  <si>
+    <t>Look for unusual traffic, auth failures, DNS anomalies, and repeated noise.</t>
+  </si>
+  <si>
+    <t>Backup check</t>
+  </si>
+  <si>
+    <t>Confirm config/log backup succeeded and storage has capacity.</t>
+  </si>
+  <si>
+    <t>Tune noisy alerts</t>
+  </si>
+  <si>
+    <t>Suppress or refine benign recurring detections with notes.</t>
+  </si>
+  <si>
+    <t>Patch cycle</t>
+  </si>
+  <si>
+    <t>Update Raspberry Pi OS, containers, and detection rules after backup.</t>
+  </si>
+  <si>
+    <t>Access review</t>
+  </si>
+  <si>
+    <t>Review SSH keys, dashboard accounts, VPN users, firewall rules.</t>
+  </si>
+  <si>
+    <t>Restore rehearsal</t>
+  </si>
+  <si>
+    <t>Test that a config backup can be restored to a safe location.</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Objective</t>
+  </si>
+  <si>
+    <t>Actions</t>
+  </si>
+  <si>
+    <t>Evidence to Preserve</t>
+  </si>
+  <si>
+    <t>Decision Point</t>
+  </si>
+  <si>
+    <t>Detect</t>
+  </si>
+  <si>
+    <t>Identify the alert and affected asset.</t>
+  </si>
+  <si>
+    <t>Record alert ID, time, source, destination, rule, and first observed activity.</t>
+  </si>
+  <si>
+    <t>Original alert, logs, packet samples if available</t>
+  </si>
+  <si>
+    <t>Is this expected activity?</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Triage</t>
+  </si>
+  <si>
+    <t>Determine severity and scope.</t>
+  </si>
+  <si>
+    <t>Check asset criticality, repeated events, auth failures, new services, and external connections.</t>
+  </si>
+  <si>
+    <t>Dashboard screenshots, raw logs, timeline notes</t>
+  </si>
+  <si>
+    <t>Benign, suspicious, or confirmed?</t>
+  </si>
+  <si>
+    <t>Contain</t>
+  </si>
+  <si>
+    <t>Limit exposure without destroying evidence.</t>
+  </si>
+  <si>
+    <t>Disconnect affected device, block path, rotate exposed credential, or pause container if needed.</t>
+  </si>
+  <si>
+    <t>Firewall change, process list, config before/after</t>
+  </si>
+  <si>
+    <t>Can monitoring continue safely?</t>
+  </si>
+  <si>
+    <t>Eradicate</t>
+  </si>
+  <si>
+    <t>Remove root cause.</t>
+  </si>
+  <si>
+    <t>Patch, remove malicious config, rebuild from known-good image, or revoke credential.</t>
+  </si>
+  <si>
+    <t>Commands run, packages changed, indicators removed</t>
+  </si>
+  <si>
+    <t>Is root cause understood?</t>
+  </si>
+  <si>
+    <t>Recover</t>
+  </si>
+  <si>
+    <t>Restore service and monitor.</t>
+  </si>
+  <si>
+    <t>Bring device back, validate logs, verify expected behavior, and watch for recurrence.</t>
+  </si>
+  <si>
+    <t>Validation checklist, service health, logs</t>
+  </si>
+  <si>
+    <t>Any recurrence?</t>
+  </si>
+  <si>
+    <t>Lessons Learned</t>
+  </si>
+  <si>
+    <t>Improve the Home SOC.</t>
+  </si>
+  <si>
+    <t>Write findings, add detections, tune dashboards, and add backlog items.</t>
+  </si>
+  <si>
+    <t>Final notes, backlog links, change log entry</t>
+  </si>
+  <si>
+    <t>What changes prevent repeat?</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>System / Service</t>
+  </si>
+  <si>
+    <t>Work Performed</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Rollback Available?</t>
+  </si>
+  <si>
+    <t>Next Action</t>
+  </si>
+  <si>
+    <t>Workbook</t>
+  </si>
+  <si>
+    <t>Created initial Home SOC operations manual.</t>
+  </si>
+  <si>
+    <t>Baseline documentation</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>Replace TBD fields with live deployment details.</t>
+  </si>
+  <si>
+    <t>Alert ID</t>
+  </si>
+  <si>
+    <t>Date/Time</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Detection / Rule</t>
+  </si>
+  <si>
+    <t>Initial Assessment</t>
+  </si>
+  <si>
+    <t>Disposition</t>
+  </si>
+  <si>
+    <t>Follow-up / Backlog Link</t>
+  </si>
+  <si>
+    <t>ALERT-0001</t>
+  </si>
+  <si>
+    <t>Informational</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Manual workbook baseline</t>
+  </si>
+  <si>
+    <t>Documentation event, no security concern.</t>
+  </si>
+  <si>
+    <t>Benign</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Credential Type</t>
+  </si>
+  <si>
+    <t>Stored Where</t>
+  </si>
+  <si>
+    <t>Rotation Cadence</t>
+  </si>
+  <si>
+    <t>Last Rotated</t>
+  </si>
+  <si>
+    <t>MFA?</t>
+  </si>
+  <si>
+    <t>Classification</t>
+  </si>
+  <si>
+    <t>Placeholder / Notes</t>
+  </si>
+  <si>
+    <t>SSH key</t>
+  </si>
+  <si>
+    <t>Password manager / key vault</t>
+  </si>
+  <si>
+    <t>Annual or on suspicion</t>
+  </si>
+  <si>
+    <t>Sensitive</t>
+  </si>
+  <si>
+    <t>Do not paste private key here.</t>
+  </si>
+  <si>
+    <t>Admin password</t>
+  </si>
+  <si>
+    <t>Password manager</t>
+  </si>
+  <si>
+    <t>Quarterly</t>
+  </si>
+  <si>
+    <t>Store only pointer/location, never secret value.</t>
+  </si>
+  <si>
+    <t>VPN</t>
+  </si>
+  <si>
+    <t>Access credential</t>
+  </si>
+  <si>
+    <t>Password manager / VPN config vault</t>
+  </si>
+  <si>
+    <t>Document recovery process separately.</t>
+  </si>
+  <si>
+    <t>API tokens</t>
+  </si>
+  <si>
+    <t>Service token</t>
+  </si>
+  <si>
+    <t>Secret manager or env file outside repo</t>
+  </si>
+  <si>
+    <t>On change</t>
+  </si>
+  <si>
+    <t>Secret Placeholder</t>
+  </si>
+  <si>
+    <t>Record token purpose and rotation date only.</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Effort</t>
+  </si>
+  <si>
+    <t>Dependencies</t>
+  </si>
+  <si>
+    <t>Current Sprint</t>
+  </si>
+  <si>
+    <t>SOC-MC-001</t>
+  </si>
+  <si>
+    <t>Keep Portainer, Netdata, and Uptime Kuma stable</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>P2 High</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Running services</t>
+  </si>
+  <si>
+    <t>Focus on reliability before adding more tools.</t>
+  </si>
+  <si>
+    <t>SOC-MC-002</t>
+  </si>
+  <si>
+    <t>Document current Docker network layout</t>
+  </si>
+  <si>
+    <t>Documentation</t>
+  </si>
+  <si>
+    <t>P3 Medium</t>
+  </si>
+  <si>
+    <t>Capture shared homesoc network details.</t>
+  </si>
+  <si>
+    <t>Next Sprint</t>
+  </si>
+  <si>
+    <t>SOC-MC-003</t>
+  </si>
+  <si>
+    <t>Decide on log collector path</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Storage and router log source</t>
+  </si>
+  <si>
+    <t>Leave collector fields blank until Loki or another solution is installed.</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>SOC-MC-005</t>
+  </si>
+  <si>
+    <t>Grafana dashboard buildout</t>
+  </si>
+  <si>
+    <t>Prometheus or other data source</t>
+  </si>
+  <si>
+    <t>Grafana is installed but paused because Netdata currently covers the need.</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>SOC-MC-006</t>
+  </si>
+  <si>
+    <t>Bring up core management and monitoring</t>
+  </si>
+  <si>
+    <t>Buildout</t>
+  </si>
+  <si>
+    <t>Raspberry Pi 4 and Docker</t>
+  </si>
+  <si>
+    <t>Portainer, Netdata, and Uptime Kuma are running.</t>
+  </si>
+  <si>
+    <t>SOC-MC-007</t>
+  </si>
+  <si>
+    <t>Prometheus is deferred</t>
+  </si>
+  <si>
+    <t>Metrics</t>
+  </si>
+  <si>
+    <t>P4 Low</t>
+  </si>
+  <si>
+    <t>Need for additional metrics backend</t>
+  </si>
+  <si>
+    <t>Revisit only when Netdata no longer meets monitoring needs.</t>
+  </si>
+  <si>
+    <t>SOC-MC-008</t>
+  </si>
+  <si>
+    <t>Wazuh remains a planned SIEM candidate</t>
+  </si>
+  <si>
+    <t>SIEM</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Lab maturity</t>
+  </si>
+  <si>
+    <t>Do not treat as installed in runbooks or service maps.</t>
+  </si>
+  <si>
+    <t>Current Lab State</t>
+  </si>
+  <si>
+    <t>Snapshot of the Raspberry Pi Home SOC components as currently documented.</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Access / Port</t>
+  </si>
+  <si>
+    <t>Core Docker host for the lab</t>
+  </si>
+  <si>
+    <t>SSH 22</t>
+  </si>
+  <si>
+    <t>Primary platform for Home SOC services.</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>Container runtime</t>
+  </si>
+  <si>
+    <t>Local host</t>
+  </si>
+  <si>
+    <t>Runs the lab services.</t>
+  </si>
+  <si>
+    <t>Container management UI</t>
+  </si>
+  <si>
+    <t>9443</t>
+  </si>
+  <si>
+    <t>Main administrative interface for containers.</t>
+  </si>
+  <si>
+    <t>Portainer Edge</t>
+  </si>
+  <si>
+    <t>Edge agent endpoint</t>
+  </si>
+  <si>
+    <t>Available</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>Included in quick reference for future/edge management.</t>
+  </si>
+  <si>
+    <t>Host and service monitoring</t>
+  </si>
+  <si>
+    <t>19999</t>
+  </si>
+  <si>
+    <t>Current monitoring dashboard for host health.</t>
+  </si>
+  <si>
+    <t>Availability monitoring</t>
+  </si>
+  <si>
+    <t>3001</t>
+  </si>
+  <si>
+    <t>Tracks service uptime and reachability.</t>
+  </si>
+  <si>
+    <t>Dashboard and visualization layer</t>
+  </si>
+  <si>
+    <t>Installed / Paused</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>Paused until Prometheus or another data source is ready.</t>
+  </si>
+  <si>
+    <t>Metrics backend</t>
+  </si>
+  <si>
+    <t>9090</t>
+  </si>
+  <si>
+    <t>Not active yet; planned for later metrics collection.</t>
+  </si>
+  <si>
+    <t>Network boundary</t>
+  </si>
+  <si>
+    <t>Primary network control point; document config exports.</t>
+  </si>
+  <si>
+    <t>Persistent storage</t>
+  </si>
+  <si>
+    <t>Track capacity and health.</t>
+  </si>
+  <si>
+    <t>Wazuh / SIEM</t>
+  </si>
+  <si>
+    <t>Security event management</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Future candidate; not installed.</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Learned</t>
+  </si>
+  <si>
+    <t>Impact / Decision</t>
+  </si>
+  <si>
+    <t>Follow-up</t>
+  </si>
+  <si>
+    <t>Portainer Stacks create isolated Docker networks.</t>
+  </si>
+  <si>
+    <t>Need to deliberately connect containers to shared networks when services should talk.</t>
+  </si>
+  <si>
+    <t>Document the homesoc network layout.</t>
+  </si>
+  <si>
+    <t>Docker networking</t>
+  </si>
+  <si>
+    <t>Connected running containers to the shared homesoc network.</t>
+  </si>
+  <si>
+    <t>Core services can be grouped without rebuilding the whole lab.</t>
+  </si>
+  <si>
+    <t>Record which services are attached to the shared network.</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Netdata alone meets current monitoring needs.</t>
+  </si>
+  <si>
+    <t>Keep Grafana paused until there is a real data-source need.</t>
+  </si>
+  <si>
+    <t>Revisit after Prometheus or another backend is added.</t>
+  </si>
+  <si>
+    <t>Roadmap discipline</t>
+  </si>
+  <si>
+    <t>Prometheus is useful, but not required yet.</t>
+  </si>
+  <si>
+    <t>Prometheus is deferred instead of pretending the stack already exists.</t>
+  </si>
+  <si>
+    <t>Move back into Current Sprint only when Grafana needs it.</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Changed By</t>
+  </si>
+  <si>
+    <t>Change Summary</t>
+  </si>
+  <si>
+    <t>Affected Sheets / Systems</t>
+  </si>
+  <si>
+    <t>Review Needed?</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>Codex for Josh</t>
+  </si>
+  <si>
+    <t>Initial Home SOC Operations Manual workbook created.</t>
+  </si>
+  <si>
+    <t>Requested baseline manual</t>
+  </si>
+  <si>
+    <t>All sheets</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>Replaced generic placeholders with actual Home SOC lab state.</t>
+  </si>
+  <si>
+    <t>Document current reality: Portainer, Netdata, Uptime Kuma, Grafana paused, CrowdSec/Wazuh planned, Prometheus deferred.</t>
+  </si>
+  <si>
+    <t>Overview; Services Containers; Network Access; Mission Control; Current Lab State; Learning Journal</t>
+  </si>
+  <si>
+    <t>Home SOC Quick Reference</t>
+  </si>
+  <si>
+    <t>Local service ports and expected access points for the Raspberry Pi Home SOC lab.</t>
+  </si>
+  <si>
+    <t>Port</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>https://&lt;raspberry-pi-ip&gt;:9443</t>
+  </si>
+  <si>
+    <t>http://&lt;raspberry-pi-ip&gt;:8000</t>
+  </si>
+  <si>
+    <t>http://&lt;raspberry-pi-ip&gt;:3000</t>
+  </si>
+  <si>
+    <t>http://&lt;raspberry-pi-ip&gt;:19999</t>
+  </si>
+  <si>
+    <t>http://&lt;raspberry-pi-ip&gt;:3001</t>
+  </si>
+  <si>
+    <t>SSH</t>
+  </si>
+  <si>
+    <t>ssh josh@&lt;raspberry-pi-ip&gt;</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>http://&lt;raspberry-pi-ip&gt;:9090</t>
+  </si>
+  <si>
+    <t>Netdata + Uptime Kuma active; Grafana paused; CrowdSec prepared/not active</t>
   </si>
   <si>
     <t>Preserve evidence before changing systems</t>
   </si>
   <si>
-    <t>Document only what exists; mark future work as Planned or Deferred.</t>
-  </si>
-  <si>
-    <t>Operating Principles</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Keep the Home SOC boring, observable, and recoverable.</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Prefer read-only monitoring where possible; document any blocking/active-response controls before enabling them.</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Do not store real passwords, API tokens, or private keys in this workbook.</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Every alert should end in one of three outcomes: benign, action taken, or backlog item.</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Back up configs before major changes and record the change in the Change Log.</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Keep Raspberry Pi patching and storage health visible; small systems fail quietly.</t>
-  </si>
-  <si>
-    <t>Asset ID</t>
-  </si>
-  <si>
-    <t>Asset Name</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>IP / Hostname</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Criticality</t>
-  </si>
-  <si>
-    <t>Backup?</t>
-  </si>
-  <si>
-    <t>Monitoring?</t>
-  </si>
-  <si>
-    <t>SOC-PI-01</t>
-  </si>
-  <si>
-    <t>Raspberry Pi SOC Host</t>
-  </si>
-  <si>
-    <t>Server</t>
-  </si>
-  <si>
-    <t>raspberrypi.local / TBD</t>
-  </si>
-  <si>
-    <t>Home LAN</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Core host for Home SOC services and logs.</t>
-  </si>
-  <si>
-    <t>NET-RTR-01</t>
-  </si>
-  <si>
-    <t>Home Router / Firewall</t>
-  </si>
-  <si>
-    <t>Network</t>
-  </si>
-  <si>
-    <t>Gateway IP TBD</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>Config export</t>
-  </si>
-  <si>
-    <t>Primary ingress/egress visibility point.</t>
-  </si>
-  <si>
-    <t>NAS-LOG-01</t>
-  </si>
-  <si>
-    <t>External SSD / Log Storage</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>Local mount TBD</t>
-  </si>
-  <si>
-    <t>Track free space and SMART/health status.</t>
-  </si>
-  <si>
-    <t>ENDPOINTS</t>
-  </si>
-  <si>
-    <t>Family Devices</t>
-  </si>
-  <si>
-    <t>Endpoint Group</t>
-  </si>
-  <si>
-    <t>DHCP range TBD</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Partial</t>
-  </si>
-  <si>
-    <t>Group record; split into devices as needed.</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Host/Container</t>
-  </si>
-  <si>
-    <t>Port(s)</t>
-  </si>
-  <si>
-    <t>Data Path</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Restart Policy</t>
-  </si>
-  <si>
-    <t>Health Check</t>
-  </si>
-  <si>
-    <t>Portainer</t>
-  </si>
-  <si>
-    <t>Docker management</t>
-  </si>
-  <si>
-    <t>Docker container</t>
-  </si>
-  <si>
-    <t>9443/TCP</t>
-  </si>
-  <si>
-    <t>Docker volume</t>
-  </si>
-  <si>
-    <t>Running</t>
-  </si>
-  <si>
-    <t>unless-stopped</t>
-  </si>
-  <si>
-    <t>Portainer UI loads</t>
-  </si>
-  <si>
-    <t>Primary management interface for lab containers.</t>
-  </si>
-  <si>
-    <t>Netdata</t>
-  </si>
-  <si>
-    <t>System monitoring and dashboard</t>
-  </si>
-  <si>
-    <t>19999/TCP</t>
-  </si>
-  <si>
-    <t>Netdata dashboard loads</t>
-  </si>
-  <si>
-    <t>Current monitoring dashboard for the Raspberry Pi host.</t>
-  </si>
-  <si>
-    <t>Uptime Kuma</t>
-  </si>
-  <si>
-    <t>Service uptime monitoring</t>
-  </si>
-  <si>
-    <t>3001/TCP</t>
-  </si>
-  <si>
-    <t>Monitors report current service state</t>
-  </si>
-  <si>
-    <t>Used to track Home SOC service availability.</t>
-  </si>
-  <si>
-    <t>Grafana</t>
-  </si>
-  <si>
-    <t>Visualization</t>
-  </si>
-  <si>
-    <t>3000/TCP</t>
-  </si>
-  <si>
-    <t>Installed (Paused)</t>
-  </si>
-  <si>
-    <t>Container installed but intentionally paused</t>
-  </si>
-  <si>
-    <t>Deferred until Prometheus or additional data sources justify it.</t>
+    <t>Document only what exists; mark future work as Planned, Prepared, or Deferred.</t>
   </si>
   <si>
     <t>CrowdSec</t>
@@ -364,946 +1279,82 @@
     <t>Threat detection and community block intelligence</t>
   </si>
   <si>
-    <t>Not installed</t>
-  </si>
-  <si>
-    <t>Planned</t>
-  </si>
-  <si>
-    <t>Install decision pending</t>
-  </si>
-  <si>
-    <t>Roadmap item; not yet part of the active lab.</t>
-  </si>
-  <si>
-    <t>Prometheus</t>
-  </si>
-  <si>
-    <t>Metrics backend for Grafana</t>
-  </si>
-  <si>
-    <t>Deferred</t>
-  </si>
-  <si>
-    <t>Deferred by design</t>
-  </si>
-  <si>
-    <t>Netdata meets current monitoring needs.</t>
-  </si>
-  <si>
-    <t>Wazuh</t>
-  </si>
-  <si>
-    <t>SIEM / endpoint security monitoring</t>
-  </si>
-  <si>
-    <t>Architecture decision pending</t>
-  </si>
-  <si>
-    <t>Future SIEM candidate; do not document as installed yet.</t>
-  </si>
-  <si>
-    <t>Path / Zone</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Destination</t>
-  </si>
-  <si>
-    <t>Protocol / Port</t>
-  </si>
-  <si>
-    <t>Allowed?</t>
-  </si>
-  <si>
-    <t>Auth Method</t>
-  </si>
-  <si>
-    <t>Logging</t>
-  </si>
-  <si>
-    <t>Risk</t>
-  </si>
-  <si>
-    <t>Review Cadence</t>
-  </si>
-  <si>
-    <t>Admin SSH</t>
-  </si>
-  <si>
-    <t>Josh admin device</t>
-  </si>
-  <si>
-    <t>SSH / 22 or custom</t>
-  </si>
-  <si>
-    <t>Key-based</t>
-  </si>
-  <si>
-    <t>Auth logs</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>Disable password SSH after key validation.</t>
-  </si>
-  <si>
-    <t>Netdata local</t>
-  </si>
-  <si>
-    <t>HTTP / 19999</t>
-  </si>
-  <si>
-    <t>Local trusted access</t>
-  </si>
-  <si>
-    <t>Netdata logs</t>
-  </si>
-  <si>
-    <t>Keep local only unless a protected access path is added.</t>
-  </si>
-  <si>
-    <t>Portainer local</t>
-  </si>
-  <si>
-    <t>HTTPS / 9443</t>
-  </si>
-  <si>
-    <t>Local account</t>
-  </si>
-  <si>
-    <t>Portainer logs</t>
-  </si>
-  <si>
-    <t>Protect carefully because it can manage containers.</t>
-  </si>
-  <si>
-    <t>Uptime Kuma local</t>
-  </si>
-  <si>
-    <t>HTTP / 3001</t>
-  </si>
-  <si>
-    <t>App logs</t>
-  </si>
-  <si>
-    <t>Used for availability checks.</t>
-  </si>
-  <si>
-    <t>Remote access</t>
-  </si>
-  <si>
-    <t>Internet</t>
-  </si>
-  <si>
-    <t>Home SOC</t>
-  </si>
-  <si>
-    <t>VPN only</t>
-  </si>
-  <si>
-    <t>MFA / keys</t>
-  </si>
-  <si>
-    <t>VPN logs</t>
-  </si>
-  <si>
-    <t>Avoid direct public dashboard exposure.</t>
-  </si>
-  <si>
-    <t>Syslog ingest</t>
-  </si>
-  <si>
-    <t>Network devices</t>
-  </si>
-  <si>
-    <t>Log collector</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>No log collector is installed yet; leave blank until Loki or another collector is selected.</t>
-  </si>
-  <si>
-    <t>Cadence</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>Procedure</t>
-  </si>
-  <si>
-    <t>Last Done</t>
-  </si>
-  <si>
-    <t>Evidence / Notes</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>Review alert queue</t>
-  </si>
-  <si>
-    <t>Check new high/critical alerts and unresolved items.</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>Check SOC host health</t>
-  </si>
-  <si>
-    <t>CPU, memory, disk, temperature, and service uptime.</t>
-  </si>
-  <si>
-    <t>Confirm log freshness</t>
-  </si>
-  <si>
-    <t>Verify latest logs arrived within expected window.</t>
-  </si>
-  <si>
-    <t>Weekly</t>
-  </si>
-  <si>
-    <t>Review dashboard trends</t>
-  </si>
-  <si>
-    <t>Look for unusual traffic, auth failures, DNS anomalies, and repeated noise.</t>
-  </si>
-  <si>
-    <t>Backup check</t>
-  </si>
-  <si>
-    <t>Confirm config/log backup succeeded and storage has capacity.</t>
-  </si>
-  <si>
-    <t>Tune noisy alerts</t>
-  </si>
-  <si>
-    <t>Suppress or refine benign recurring detections with notes.</t>
-  </si>
-  <si>
-    <t>Patch cycle</t>
-  </si>
-  <si>
-    <t>Update Raspberry Pi OS, containers, and detection rules after backup.</t>
-  </si>
-  <si>
-    <t>Access review</t>
-  </si>
-  <si>
-    <t>Review SSH keys, dashboard accounts, VPN users, firewall rules.</t>
-  </si>
-  <si>
-    <t>Restore rehearsal</t>
-  </si>
-  <si>
-    <t>Test that a config backup can be restored to a safe location.</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Objective</t>
-  </si>
-  <si>
-    <t>Actions</t>
-  </si>
-  <si>
-    <t>Evidence to Preserve</t>
-  </si>
-  <si>
-    <t>Decision Point</t>
-  </si>
-  <si>
-    <t>Detect</t>
-  </si>
-  <si>
-    <t>Identify the alert and affected asset.</t>
-  </si>
-  <si>
-    <t>Record alert ID, time, source, destination, rule, and first observed activity.</t>
-  </si>
-  <si>
-    <t>Original alert, logs, packet samples if available</t>
-  </si>
-  <si>
-    <t>Is this expected activity?</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Triage</t>
-  </si>
-  <si>
-    <t>Determine severity and scope.</t>
-  </si>
-  <si>
-    <t>Check asset criticality, repeated events, auth failures, new services, and external connections.</t>
-  </si>
-  <si>
-    <t>Dashboard screenshots, raw logs, timeline notes</t>
-  </si>
-  <si>
-    <t>Benign, suspicious, or confirmed?</t>
-  </si>
-  <si>
-    <t>Contain</t>
-  </si>
-  <si>
-    <t>Limit exposure without destroying evidence.</t>
-  </si>
-  <si>
-    <t>Disconnect affected device, block path, rotate exposed credential, or pause container if needed.</t>
-  </si>
-  <si>
-    <t>Firewall change, process list, config before/after</t>
-  </si>
-  <si>
-    <t>Can monitoring continue safely?</t>
-  </si>
-  <si>
-    <t>Eradicate</t>
-  </si>
-  <si>
-    <t>Remove root cause.</t>
-  </si>
-  <si>
-    <t>Patch, remove malicious config, rebuild from known-good image, or revoke credential.</t>
-  </si>
-  <si>
-    <t>Commands run, packages changed, indicators removed</t>
-  </si>
-  <si>
-    <t>Is root cause understood?</t>
-  </si>
-  <si>
-    <t>Recover</t>
-  </si>
-  <si>
-    <t>Restore service and monitor.</t>
-  </si>
-  <si>
-    <t>Bring device back, validate logs, verify expected behavior, and watch for recurrence.</t>
-  </si>
-  <si>
-    <t>Validation checklist, service health, logs</t>
-  </si>
-  <si>
-    <t>Any recurrence?</t>
-  </si>
-  <si>
-    <t>Lessons Learned</t>
-  </si>
-  <si>
-    <t>Improve the Home SOC.</t>
-  </si>
-  <si>
-    <t>Write findings, add detections, tune dashboards, and add backlog items.</t>
-  </si>
-  <si>
-    <t>Final notes, backlog links, change log entry</t>
-  </si>
-  <si>
-    <t>What changes prevent repeat?</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>System / Service</t>
-  </si>
-  <si>
-    <t>Work Performed</t>
-  </si>
-  <si>
-    <t>Reason</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Rollback Available?</t>
-  </si>
-  <si>
-    <t>Next Action</t>
-  </si>
-  <si>
-    <t>Workbook</t>
-  </si>
-  <si>
-    <t>Created initial Home SOC operations manual.</t>
-  </si>
-  <si>
-    <t>Baseline documentation</t>
-  </si>
-  <si>
-    <t>Complete</t>
-  </si>
-  <si>
-    <t>Replace TBD fields with live deployment details.</t>
-  </si>
-  <si>
-    <t>Alert ID</t>
-  </si>
-  <si>
-    <t>Date/Time</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Detection / Rule</t>
-  </si>
-  <si>
-    <t>Initial Assessment</t>
-  </si>
-  <si>
-    <t>Disposition</t>
-  </si>
-  <si>
-    <t>Follow-up / Backlog Link</t>
-  </si>
-  <si>
-    <t>ALERT-0001</t>
-  </si>
-  <si>
-    <t>Informational</t>
-  </si>
-  <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
-    <t>Manual workbook baseline</t>
-  </si>
-  <si>
-    <t>Documentation event, no security concern.</t>
-  </si>
-  <si>
-    <t>Benign</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>Credential Type</t>
-  </si>
-  <si>
-    <t>Stored Where</t>
-  </si>
-  <si>
-    <t>Rotation Cadence</t>
-  </si>
-  <si>
-    <t>Last Rotated</t>
-  </si>
-  <si>
-    <t>MFA?</t>
-  </si>
-  <si>
-    <t>Classification</t>
-  </si>
-  <si>
-    <t>Placeholder / Notes</t>
-  </si>
-  <si>
-    <t>SSH key</t>
-  </si>
-  <si>
-    <t>Password manager / key vault</t>
-  </si>
-  <si>
-    <t>Annual or on suspicion</t>
-  </si>
-  <si>
-    <t>Sensitive</t>
-  </si>
-  <si>
-    <t>Do not paste private key here.</t>
-  </si>
-  <si>
-    <t>Admin password</t>
-  </si>
-  <si>
-    <t>Password manager</t>
-  </si>
-  <si>
-    <t>Quarterly</t>
-  </si>
-  <si>
-    <t>Store only pointer/location, never secret value.</t>
-  </si>
-  <si>
-    <t>VPN</t>
-  </si>
-  <si>
-    <t>Access credential</t>
-  </si>
-  <si>
-    <t>Password manager / VPN config vault</t>
-  </si>
-  <si>
-    <t>Document recovery process separately.</t>
-  </si>
-  <si>
-    <t>API tokens</t>
-  </si>
-  <si>
-    <t>Service token</t>
-  </si>
-  <si>
-    <t>Secret manager or env file outside repo</t>
-  </si>
-  <si>
-    <t>On change</t>
-  </si>
-  <si>
-    <t>Secret Placeholder</t>
-  </si>
-  <si>
-    <t>Record token purpose and rotation date only.</t>
-  </si>
-  <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Effort</t>
-  </si>
-  <si>
-    <t>Dependencies</t>
-  </si>
-  <si>
-    <t>Current Sprint</t>
-  </si>
-  <si>
-    <t>SOC-MC-001</t>
-  </si>
-  <si>
-    <t>Keep Portainer, Netdata, and Uptime Kuma stable</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>P2 High</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Running services</t>
-  </si>
-  <si>
-    <t>Focus on reliability before adding more tools.</t>
-  </si>
-  <si>
-    <t>SOC-MC-002</t>
-  </si>
-  <si>
-    <t>Document current Docker network layout</t>
-  </si>
-  <si>
-    <t>Documentation</t>
-  </si>
-  <si>
-    <t>P3 Medium</t>
-  </si>
-  <si>
-    <t>Capture shared homesoc network details.</t>
-  </si>
-  <si>
-    <t>Next Sprint</t>
-  </si>
-  <si>
-    <t>SOC-MC-003</t>
-  </si>
-  <si>
-    <t>Decide on log collector path</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Storage and router log source</t>
-  </si>
-  <si>
-    <t>Leave collector fields blank until Loki or another solution is installed.</t>
+    <t>Docker Compose service</t>
+  </si>
+  <si>
+    <t>127.0.0.1:8080 -&gt; 8080/TCP</t>
+  </si>
+  <si>
+    <t>Named Docker volumes</t>
+  </si>
+  <si>
+    <t>Prepared / Not Active</t>
+  </si>
+  <si>
+    <t>Pending docker compose config on Pi</t>
+  </si>
+  <si>
+    <t>Prepared under docker/crowdsec; detection-only, no bouncer or blocking enabled.</t>
+  </si>
+  <si>
+    <t>CrowdSec LAPI</t>
+  </si>
+  <si>
+    <t>SOC-PI-01 localhost</t>
+  </si>
+  <si>
+    <t>HTTP / 127.0.0.1:8080</t>
+  </si>
+  <si>
+    <t>Prepared</t>
+  </si>
+  <si>
+    <t>Local API</t>
+  </si>
+  <si>
+    <t>CrowdSec logs</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Loopback-only Compose mapping; not active until deployed.</t>
   </si>
   <si>
     <t>SOC-MC-004</t>
   </si>
   <si>
-    <t>Evaluate CrowdSec install</t>
+    <t>Validate and deploy prepared CrowdSec Compose stack</t>
   </si>
   <si>
     <t>Detection</t>
   </si>
   <si>
-    <t>Stable baseline monitoring</t>
-  </si>
-  <si>
-    <t>Planned, not active.</t>
-  </si>
-  <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>SOC-MC-005</t>
-  </si>
-  <si>
-    <t>Grafana dashboard buildout</t>
-  </si>
-  <si>
-    <t>Prometheus or other data source</t>
-  </si>
-  <si>
-    <t>Grafana is installed but paused because Netdata currently covers the need.</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>SOC-MC-006</t>
-  </si>
-  <si>
-    <t>Bring up core management and monitoring</t>
-  </si>
-  <si>
-    <t>Buildout</t>
-  </si>
-  <si>
-    <t>Raspberry Pi 4 and Docker</t>
-  </si>
-  <si>
-    <t>Portainer, Netdata, and Uptime Kuma are running.</t>
-  </si>
-  <si>
-    <t>SOC-MC-007</t>
-  </si>
-  <si>
-    <t>Prometheus is deferred</t>
-  </si>
-  <si>
-    <t>Metrics</t>
-  </si>
-  <si>
-    <t>P4 Low</t>
-  </si>
-  <si>
-    <t>Need for additional metrics backend</t>
-  </si>
-  <si>
-    <t>Revisit only when Netdata no longer meets monitoring needs.</t>
-  </si>
-  <si>
-    <t>SOC-MC-008</t>
-  </si>
-  <si>
-    <t>Wazuh remains a planned SIEM candidate</t>
-  </si>
-  <si>
-    <t>SIEM</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Lab maturity</t>
-  </si>
-  <si>
-    <t>Do not treat as installed in runbooks or service maps.</t>
-  </si>
-  <si>
-    <t>Current Lab State</t>
-  </si>
-  <si>
-    <t>Snapshot of the Raspberry Pi Home SOC components as currently documented.</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Access / Port</t>
-  </si>
-  <si>
-    <t>Core Docker host for the lab</t>
-  </si>
-  <si>
-    <t>SSH 22</t>
-  </si>
-  <si>
-    <t>Primary platform for Home SOC services.</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>Container runtime</t>
-  </si>
-  <si>
-    <t>Local host</t>
-  </si>
-  <si>
-    <t>Runs the lab services.</t>
-  </si>
-  <si>
-    <t>Container management UI</t>
-  </si>
-  <si>
-    <t>9443</t>
-  </si>
-  <si>
-    <t>Main administrative interface for containers.</t>
-  </si>
-  <si>
-    <t>Portainer Edge</t>
-  </si>
-  <si>
-    <t>Edge agent endpoint</t>
-  </si>
-  <si>
-    <t>Available</t>
-  </si>
-  <si>
-    <t>8000</t>
-  </si>
-  <si>
-    <t>Included in quick reference for future/edge management.</t>
-  </si>
-  <si>
-    <t>Host and service monitoring</t>
-  </si>
-  <si>
-    <t>19999</t>
-  </si>
-  <si>
-    <t>Current monitoring dashboard for host health.</t>
-  </si>
-  <si>
-    <t>Availability monitoring</t>
-  </si>
-  <si>
-    <t>3001</t>
-  </si>
-  <si>
-    <t>Tracks service uptime and reachability.</t>
-  </si>
-  <si>
-    <t>Dashboard and visualization layer</t>
-  </si>
-  <si>
-    <t>Installed / Paused</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>Paused until Prometheus or another data source is ready.</t>
-  </si>
-  <si>
-    <t>Metrics backend</t>
-  </si>
-  <si>
-    <t>9090</t>
-  </si>
-  <si>
-    <t>Not active yet; planned for later metrics collection.</t>
-  </si>
-  <si>
-    <t>Network boundary</t>
-  </si>
-  <si>
-    <t>Primary network control point; document config exports.</t>
-  </si>
-  <si>
-    <t>Persistent storage</t>
-  </si>
-  <si>
-    <t>Track capacity and health.</t>
-  </si>
-  <si>
-    <t>Wazuh / SIEM</t>
-  </si>
-  <si>
-    <t>Security event management</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Future candidate; not installed.</t>
-  </si>
-  <si>
-    <t>Threat intelligence and blocking</t>
-  </si>
-  <si>
-    <t>Future candidate; document before enabling active blocking.</t>
-  </si>
-  <si>
-    <t>Topic</t>
-  </si>
-  <si>
-    <t>Learned</t>
-  </si>
-  <si>
-    <t>Impact / Decision</t>
-  </si>
-  <si>
-    <t>Follow-up</t>
-  </si>
-  <si>
-    <t>Portainer Stacks create isolated Docker networks.</t>
-  </si>
-  <si>
-    <t>Need to deliberately connect containers to shared networks when services should talk.</t>
-  </si>
-  <si>
-    <t>Document the homesoc network layout.</t>
-  </si>
-  <si>
-    <t>Docker networking</t>
-  </si>
-  <si>
-    <t>Connected running containers to the shared homesoc network.</t>
-  </si>
-  <si>
-    <t>Core services can be grouped without rebuilding the whole lab.</t>
-  </si>
-  <si>
-    <t>Record which services are attached to the shared network.</t>
-  </si>
-  <si>
-    <t>Monitoring</t>
-  </si>
-  <si>
-    <t>Netdata alone meets current monitoring needs.</t>
-  </si>
-  <si>
-    <t>Keep Grafana paused until there is a real data-source need.</t>
-  </si>
-  <si>
-    <t>Revisit after Prometheus or another backend is added.</t>
-  </si>
-  <si>
-    <t>Roadmap discipline</t>
-  </si>
-  <si>
-    <t>Prometheus is useful, but not required yet.</t>
-  </si>
-  <si>
-    <t>Prometheus is deferred instead of pretending the stack already exists.</t>
-  </si>
-  <si>
-    <t>Move back into Current Sprint only when Grafana needs it.</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Changed By</t>
-  </si>
-  <si>
-    <t>Change Summary</t>
-  </si>
-  <si>
-    <t>Affected Sheets / Systems</t>
-  </si>
-  <si>
-    <t>Review Needed?</t>
-  </si>
-  <si>
-    <t>Approved By</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>Codex for Josh</t>
-  </si>
-  <si>
-    <t>Initial Home SOC Operations Manual workbook created.</t>
-  </si>
-  <si>
-    <t>Requested baseline manual</t>
-  </si>
-  <si>
-    <t>All sheets</t>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>Replaced generic placeholders with actual Home SOC lab state.</t>
-  </si>
-  <si>
-    <t>Document current reality: Portainer, Netdata, Uptime Kuma, Grafana paused, CrowdSec/Wazuh planned, Prometheus deferred.</t>
-  </si>
-  <si>
-    <t>Overview; Services Containers; Network Access; Mission Control; Current Lab State; Learning Journal</t>
-  </si>
-  <si>
-    <t>Home SOC Quick Reference</t>
-  </si>
-  <si>
-    <t>Local service ports and expected access points for the Raspberry Pi Home SOC lab.</t>
-  </si>
-  <si>
-    <t>Port</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>https://&lt;raspberry-pi-ip&gt;:9443</t>
-  </si>
-  <si>
-    <t>http://&lt;raspberry-pi-ip&gt;:8000</t>
-  </si>
-  <si>
-    <t>http://&lt;raspberry-pi-ip&gt;:3000</t>
-  </si>
-  <si>
-    <t>http://&lt;raspberry-pi-ip&gt;:19999</t>
-  </si>
-  <si>
-    <t>http://&lt;raspberry-pi-ip&gt;:3001</t>
-  </si>
-  <si>
-    <t>SSH</t>
-  </si>
-  <si>
-    <t>ssh josh@&lt;raspberry-pi-ip&gt;</t>
-  </si>
-  <si>
-    <t>Enabled</t>
-  </si>
-  <si>
-    <t>http://&lt;raspberry-pi-ip&gt;:9090</t>
+    <t>homesoc Docker network; Pi Compose validation</t>
+  </si>
+  <si>
+    <t>Prepared, not active. Deploy with Docker Compose, not Portainer.</t>
+  </si>
+  <si>
+    <t>Threat intelligence and detection</t>
+  </si>
+  <si>
+    <t>Docker Compose deployment ready under docker/crowdsec; no bouncer or blocking configured.</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>Recorded prepared CrowdSec Docker Compose deployment details.</t>
+  </si>
+  <si>
+    <t>Align workbook with repository deployment files without claiming active service state.</t>
+  </si>
+  <si>
+    <t>Services Containers; Network Access; Mission Control; Current Lab State; Quick Reference</t>
+  </si>
+  <si>
+    <t>http://127.0.0.1:8080</t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1365,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1365,8 +1416,24 @@
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7F6000"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1403,8 +1470,23 @@
         <fgColor rgb="FF5B9BD5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1644,11 +1726,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7E1CD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7E1CD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7E1CD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7E1CD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1762,17 +1859,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1784,6 +1881,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1799,7 +1908,7 @@
         <color rgb="FF833C0C"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
@@ -1810,7 +1919,7 @@
         <color rgb="FF7F6000"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
@@ -1821,7 +1930,7 @@
         <color rgb="FF375623"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
@@ -1832,7 +1941,7 @@
         <color rgb="FF833C0C"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
@@ -1843,7 +1952,7 @@
         <color rgb="FF7F6000"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
@@ -1854,7 +1963,7 @@
         <color rgb="FF375623"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
@@ -2006,6 +2115,53 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Text Box 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noGrp="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2024,7 +2180,7 @@
         <xdr:cNvPr id="1026" name="Text Box 2" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A5C34E2-F103-9FFA-3F62-74B333D6AB66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEE90DE3-2B52-4545-CCF7-0BB17765340F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2472,30 +2628,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
     </row>
     <row r="2" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1"/>
@@ -2555,13 +2711,13 @@
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="6" t="s">
-        <v>15</v>
+        <v>403</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>16</v>
+        <v>404</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>17</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2576,8 +2732,8 @@
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="42" t="s">
-        <v>18</v>
+      <c r="A7" s="50" t="s">
+        <v>15</v>
       </c>
       <c r="B7" s="43"/>
       <c r="C7" s="43"/>
@@ -2590,10 +2746,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" s="43"/>
       <c r="D8" s="43"/>
@@ -2605,10 +2761,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="43"/>
       <c r="D9" s="43"/>
@@ -2620,10 +2776,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C10" s="43"/>
       <c r="D10" s="43"/>
@@ -2635,10 +2791,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
@@ -2650,10 +2806,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
@@ -2665,10 +2821,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C13" s="45"/>
       <c r="D13" s="45"/>
@@ -2715,28 +2871,28 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="12" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>10</v>
@@ -2744,176 +2900,176 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="H4" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="I4" s="17" t="s">
         <v>280</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="15" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="G5" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="17" t="s">
         <v>285</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="27">
       <c r="A6" s="15" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="27">
       <c r="A7" s="15" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>299</v>
+        <v>422</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>300</v>
+        <v>423</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>301</v>
+        <v>424</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>104</v>
+        <v>411</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>302</v>
+        <v>425</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>303</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="27">
       <c r="A8" s="15" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="G8" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="I8" s="17" t="s">
         <v>296</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="15" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2921,28 +3077,28 @@
         <v>10</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2950,28 +3106,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3000,46 +3156,47 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="23.75" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="6" max="6" width="52.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.1" customHeight="1">
-      <c r="A1" s="47" t="s">
-        <v>327</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="A1" s="51" t="s">
+        <v>315</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
     </row>
     <row r="2" spans="1:6" ht="26.1" customHeight="1">
-      <c r="A2" s="48" t="s">
-        <v>328</v>
-      </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
+      <c r="A2" s="52" t="s">
+        <v>316</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="29" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F4" s="31" t="s">
         <v>10</v>
@@ -3047,242 +3204,242 @@
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="37" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="E5" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="37" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="E6" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="E7" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
       <c r="A8" s="37" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="37" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="A10" s="37" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="E10" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
       <c r="A11" s="37" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
       <c r="A12" s="37" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="E12" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="26.45" customHeight="1">
       <c r="A13" s="37" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E13" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="26.45" customHeight="1">
       <c r="A14" s="37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E14" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1">
       <c r="A15" s="37" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="E15" s="28" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="34.5" customHeight="1">
       <c r="A16" s="38" t="s">
-        <v>101</v>
+        <v>406</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>368</v>
+        <v>427</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>104</v>
+        <v>411</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="E16" s="33" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>369</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -3324,19 +3481,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27">
@@ -3344,16 +3501,16 @@
         <v>46235</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3361,16 +3518,16 @@
         <v>46236</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3378,16 +3535,16 @@
         <v>46236</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="27">
@@ -3395,16 +3552,16 @@
         <v>46236</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4806,51 +4963,51 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="12" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="15" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="B4" s="21">
         <v>46235</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>11</v>
@@ -4858,39 +5015,55 @@
     </row>
     <row r="5" spans="1:8" ht="54">
       <c r="A5" s="18" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="B5" s="22">
         <v>46236.068598622682</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H5" s="20" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" s="23">
+        <v>46243.708333333336</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -6877,7 +7050,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -6887,131 +7060,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25">
-      <c r="A1" s="47" t="s">
-        <v>404</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="A1" s="51" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="48" t="s">
-        <v>405</v>
-      </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
+      <c r="A2" s="52" t="s">
+        <v>391</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="29" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="52.7" customHeight="1">
       <c r="A5" s="37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B5" s="35">
         <v>9443</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="39.6" customHeight="1">
       <c r="A6" s="37" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B6" s="35">
         <v>8000</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="39.6" customHeight="1">
       <c r="A7" s="37" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B7" s="35">
         <v>3000</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="52.7" customHeight="1">
       <c r="A8" s="37" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B8" s="35">
         <v>19999</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="39.6" customHeight="1">
       <c r="A9" s="37" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B9" s="35">
         <v>3001</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="52.7" customHeight="1">
       <c r="A10" s="37" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B10" s="35">
         <v>22</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="39.6" customHeight="1">
       <c r="A11" s="38" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B11" s="36">
         <v>9090</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A12" s="41" t="s">
+        <v>414</v>
+      </c>
+      <c r="B12" s="40">
+        <v>8080</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -7034,7 +7221,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355EC953-A536-496B-A676-3DB20F0B5F50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
@@ -7062,31 +7249,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="H3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="I3" s="13" t="s">
         <v>36</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="J3" s="14" t="s">
         <v>10</v>
@@ -7094,130 +7281,130 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>40</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>43</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="17" t="s">
         <v>44</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>48</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>51</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>55</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>60</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>63</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G7" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="20" t="s">
         <v>64</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" s="20" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -7270,31 +7457,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="H3" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="I3" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J3" s="14" t="s">
         <v>10</v>
@@ -7302,208 +7489,214 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="E4" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="F4" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="G4" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="H4" s="16" t="s">
         <v>80</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>83</v>
       </c>
       <c r="I4" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="16" t="s">
         <v>85</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>88</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>90</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="27">
       <c r="A7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="G7" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>96</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>99</v>
       </c>
       <c r="I7" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="27">
       <c r="A8" s="15" t="s">
-        <v>101</v>
+        <v>406</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>102</v>
+        <v>407</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+        <v>408</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>410</v>
+      </c>
       <c r="F8" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="16"/>
+        <v>411</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>79</v>
+      </c>
       <c r="H8" s="16" t="s">
-        <v>105</v>
+        <v>412</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>106</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="15" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="18" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
       <c r="F10" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G10" s="19"/>
       <c r="H10" s="19" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I10" s="19" t="s">
         <v>11</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -7521,7 +7714,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7541,31 +7734,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="I3" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>124</v>
       </c>
       <c r="J3" s="14" t="s">
         <v>10</v>
@@ -7573,192 +7766,224 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="15" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="15" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="15" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="15" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="27">
       <c r="A9" s="18" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>157</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="33" customHeight="1">
+      <c r="A10" s="39" t="s">
+        <v>414</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>415</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>419</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>420</v>
+      </c>
+      <c r="I10" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="39" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -7805,194 +8030,194 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="12" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="15" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F4" s="21"/>
       <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="15" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F5" s="21"/>
       <c r="G5" s="17"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>163</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>170</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F6" s="21"/>
       <c r="G6" s="17"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="15" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F7" s="21"/>
       <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="15" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F8" s="21"/>
       <c r="G8" s="17"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="15" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="15" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F10" s="21"/>
       <c r="G10" s="17"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="15" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F11" s="21"/>
       <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="18" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="20"/>
@@ -9751,163 +9976,163 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="12" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27">
       <c r="A5" s="15" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="27">
       <c r="A6" s="15" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="27">
       <c r="A7" s="15" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27">
       <c r="A8" s="15" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>11</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="18" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -9942,28 +10167,28 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -9971,25 +10196,25 @@
         <v>46236.068598449077</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G4" s="19" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -12016,66 +12241,66 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="12" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="18" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B4" s="25">
         <v>46236.068598460646</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="I4" s="19" t="s">
         <v>11</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -15709,139 +15934,139 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>245</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F4" s="21"/>
       <c r="G4" s="16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="15" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F5" s="21"/>
       <c r="G5" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="15" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F6" s="21"/>
       <c r="G6" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="18" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="F7" s="22"/>
       <c r="G7" s="19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:9">
